--- a/ci-cd-merge-resolver/repoCollector/datasets/iotdb.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/iotdb.xlsx
@@ -44,28 +44,82 @@
     <t>isMultiModule</t>
   </si>
   <si>
+    <t>524c9fe9e7951154f95280241ce42f1d29f8614a</t>
+  </si>
+  <si>
+    <t>871fce07425022ad5569a0b0186b0563f3a4542f</t>
+  </si>
+  <si>
+    <t>2cbee31e19f563d5c688d119056da9e9ff582d40</t>
+  </si>
+  <si>
+    <t>39235aa922a32abdb02e9cf4a695461b50570739</t>
+  </si>
+  <si>
+    <t>0ed3f9f9e5c5e6a3767a19c0bc306e028e64535b</t>
+  </si>
+  <si>
+    <t>acd8039bd11c6253a468a772f8d0f937a5d1f79f</t>
+  </si>
+  <si>
+    <t>8466408fc223a8577606bf00c9923950002902af</t>
+  </si>
+  <si>
+    <t>64830328d7895f70fded8e4192c6beb3ff8c0791</t>
+  </si>
+  <si>
+    <t>d08b08672cc7c622a68a529312475388d82c63e9</t>
+  </si>
+  <si>
+    <t>a64002ad82130ccf7d746b34b310db5ead8c7562</t>
+  </si>
+  <si>
+    <t>b68bc1935aab8c53394065d968324a247a538645</t>
+  </si>
+  <si>
+    <t>6510a20c6f668bbd1555ada154fdaf12b98dc88b</t>
+  </si>
+  <si>
+    <t>759629450f812279c94aa078b72ebf22b72fc728</t>
+  </si>
+  <si>
     <t>c6abcb9c62e7fb113f36d50067d3c21a57617627</t>
   </si>
   <si>
+    <t>96f72bf71306e328fc99368c6be69005e50f8542</t>
+  </si>
+  <si>
+    <t>de6130e27bf62bf5d765159e58174c4d6441ecbd</t>
+  </si>
+  <si>
+    <t>ea534cf2d97afa88cf1c6e6fc5cc4443cd32ebcd</t>
+  </si>
+  <si>
+    <t>e4801d90869cbf1884b2ab73398cac118ffb285d</t>
+  </si>
+  <si>
+    <t>b01f724fd94ef06bc2f93865a6085ea4bb6e49f5</t>
+  </si>
+  <si>
+    <t>b44f46afb727e8e2525729d2a648d47761c7a4b7</t>
+  </si>
+  <si>
+    <t>ab5f7ccdf656120a46f23b8c6ef85f563a1673e5</t>
+  </si>
+  <si>
     <t>0b81e0b2f73047ca99626c2e2efb22c8619d3309</t>
   </si>
   <si>
     <t>c2216eb9bd617c16062ad696d86d944615e6c74d</t>
   </si>
   <si>
-    <t>39235aa922a32abdb02e9cf4a695461b50570739</t>
-  </si>
-  <si>
-    <t>0ed3f9f9e5c5e6a3767a19c0bc306e028e64535b</t>
-  </si>
-  <si>
-    <t>acd8039bd11c6253a468a772f8d0f937a5d1f79f</t>
-  </si>
-  <si>
-    <t>759629450f812279c94aa078b72ebf22b72fc728</t>
-  </si>
-  <si>
-    <t>6510a20c6f668bbd1555ada154fdaf12b98dc88b</t>
+    <t>050ede8d1640cd8737b2988c89293c541e439eb9</t>
+  </si>
+  <si>
+    <t>431d6a450dd73fcf131738eaf5d1b0b5b4921020</t>
+  </si>
+  <si>
+    <t>97e3b6d1bcae9de7a0d86198ac1fe62ebe272b30</t>
   </si>
   <si>
     <t>0115a9ace2e526f4bcdf3a399a92732ef32ad184</t>
@@ -77,15 +131,99 @@
     <t>b2d88da9ba7eb1e48e0addaeef2f32bd30cf0df4</t>
   </si>
   <si>
+    <t>6d06e32079ce995632790fbd90775ad66966d184</t>
+  </si>
+  <si>
+    <t>1572237cdd26a698e224b10029f4b010e696bb07</t>
+  </si>
+  <si>
+    <t>7cd97bce0386b63648bf7c969753b13121a19396</t>
+  </si>
+  <si>
+    <t>735977ee7c6fc0af70b43ec6c2b2d3e23206d14a</t>
+  </si>
+  <si>
+    <t>fda05aac611a7ed8144cb3d6dfe2bb513d07500b</t>
+  </si>
+  <si>
+    <t>6df3d4354ac5f07e0a3df627b085a8d3dccf93c5</t>
+  </si>
+  <si>
+    <t>2c2c93c7f9894ac253e2305e243f8693d6afe16a</t>
+  </si>
+  <si>
+    <t>66226ee68a860cda6530d2869ec7330ac3f2b11d</t>
+  </si>
+  <si>
+    <t>46fbb66cbda0e630a8c574d72316821a41f9d568</t>
+  </si>
+  <si>
+    <t>97f2bdac9fcc37144ff88d852282d5064abfcfeb</t>
+  </si>
+  <si>
+    <t>c2a8bee1d8c4ac8aac7b80bccefceb757dd63b97</t>
+  </si>
+  <si>
+    <t>0bc56c4c29bfd4906a9467bddc102bd07482c159</t>
+  </si>
+  <si>
+    <t>f74a588a95a5fa9fe8cd10cebc9b81dd5eb96c9e</t>
+  </si>
+  <si>
+    <t>e8a41111c42cfd2b5309262d1873ef8cbcbc4536</t>
+  </si>
+  <si>
+    <t>03fbb9e7e1c729547cee2cf6fd840707f8ff70b7</t>
+  </si>
+  <si>
+    <t>4d62d50450b988eb591c73582d1488e48ebcb19e</t>
+  </si>
+  <si>
+    <t>0f9b797fb9b72e3b8599f45119ddfecae65609a5</t>
+  </si>
+  <si>
+    <t>a3646a34d70c1a91c80578a2c735a7cf4f488523</t>
+  </si>
+  <si>
+    <t>6bcdce6703462b574477bce0b455dd22a00e16ea</t>
+  </si>
+  <si>
+    <t>60565b346279343051032a0a004f55306f3fe488</t>
+  </si>
+  <si>
+    <t>40ae1e9fa1f50056bf51c61c2ffef38e8ad80253</t>
+  </si>
+  <si>
+    <t>96b78f4f09ba63e66cadbe23e803bbe48ed94c2f</t>
+  </si>
+  <si>
+    <t>ea12c00d132de50663a92a98bc46c652d99abbcf</t>
+  </si>
+  <si>
+    <t>616a604885fc4d157359b768337c921223bd7fd2</t>
+  </si>
+  <si>
+    <t>d193a0c3876a52af0e1f2ab0d9b8d90e9baedcbd</t>
+  </si>
+  <si>
+    <t>de3a1740aef08a4f443bd0e23c8a6745d412a49d</t>
+  </si>
+  <si>
     <t>9a4a49c3774d18b48682c4fd90ae4bdefa852233</t>
   </si>
   <si>
-    <t>4d62d50450b988eb591c73582d1488e48ebcb19e</t>
-  </si>
-  <si>
     <t>f94d326fe62ec7f8ac8ee6121df25009b104b762</t>
   </si>
   <si>
+    <t>22dbf13ac8bd607ddae4cfa46793c6e2c47ef9d8</t>
+  </si>
+  <si>
+    <t>f8bed884765988bbbbf64db9bbfc0b35174ff2a8</t>
+  </si>
+  <si>
+    <t>e1d4660f6387492fcd4f81bb0df60bc611858131</t>
+  </si>
+  <si>
     <t>933537cdd2d287cbd99abf262ea915fb3e4fdb4c</t>
   </si>
   <si>
@@ -95,30 +233,6 @@
     <t>32d3f90e02ebd0e89322f751aafec8e694beae0e</t>
   </si>
   <si>
-    <t>6d06e32079ce995632790fbd90775ad66966d184</t>
-  </si>
-  <si>
-    <t>1572237cdd26a698e224b10029f4b010e696bb07</t>
-  </si>
-  <si>
-    <t>7cd97bce0386b63648bf7c969753b13121a19396</t>
-  </si>
-  <si>
-    <t>a64002ad82130ccf7d746b34b310db5ead8c7562</t>
-  </si>
-  <si>
-    <t>b68bc1935aab8c53394065d968324a247a538645</t>
-  </si>
-  <si>
-    <t>b01f724fd94ef06bc2f93865a6085ea4bb6e49f5</t>
-  </si>
-  <si>
-    <t>b44f46afb727e8e2525729d2a648d47761c7a4b7</t>
-  </si>
-  <si>
-    <t>ab5f7ccdf656120a46f23b8c6ef85f563a1673e5</t>
-  </si>
-  <si>
     <t>cf5f441224d7f652cc2801b41a97f8ed8e4b3592</t>
   </si>
   <si>
@@ -128,96 +242,6 @@
     <t>dedcd42c965278bc898db5eb3ac95a9fe05360db</t>
   </si>
   <si>
-    <t>8466408fc223a8577606bf00c9923950002902af</t>
-  </si>
-  <si>
-    <t>64830328d7895f70fded8e4192c6beb3ff8c0791</t>
-  </si>
-  <si>
-    <t>d08b08672cc7c622a68a529312475388d82c63e9</t>
-  </si>
-  <si>
-    <t>22dbf13ac8bd607ddae4cfa46793c6e2c47ef9d8</t>
-  </si>
-  <si>
-    <t>f8bed884765988bbbbf64db9bbfc0b35174ff2a8</t>
-  </si>
-  <si>
-    <t>e1d4660f6387492fcd4f81bb0df60bc611858131</t>
-  </si>
-  <si>
-    <t>524c9fe9e7951154f95280241ce42f1d29f8614a</t>
-  </si>
-  <si>
-    <t>871fce07425022ad5569a0b0186b0563f3a4542f</t>
-  </si>
-  <si>
-    <t>2cbee31e19f563d5c688d119056da9e9ff582d40</t>
-  </si>
-  <si>
-    <t>050ede8d1640cd8737b2988c89293c541e439eb9</t>
-  </si>
-  <si>
-    <t>431d6a450dd73fcf131738eaf5d1b0b5b4921020</t>
-  </si>
-  <si>
-    <t>97e3b6d1bcae9de7a0d86198ac1fe62ebe272b30</t>
-  </si>
-  <si>
-    <t>96b78f4f09ba63e66cadbe23e803bbe48ed94c2f</t>
-  </si>
-  <si>
-    <t>ea12c00d132de50663a92a98bc46c652d99abbcf</t>
-  </si>
-  <si>
-    <t>616a604885fc4d157359b768337c921223bd7fd2</t>
-  </si>
-  <si>
-    <t>f74a588a95a5fa9fe8cd10cebc9b81dd5eb96c9e</t>
-  </si>
-  <si>
-    <t>e8a41111c42cfd2b5309262d1873ef8cbcbc4536</t>
-  </si>
-  <si>
-    <t>03fbb9e7e1c729547cee2cf6fd840707f8ff70b7</t>
-  </si>
-  <si>
-    <t>0f9b797fb9b72e3b8599f45119ddfecae65609a5</t>
-  </si>
-  <si>
-    <t>a3646a34d70c1a91c80578a2c735a7cf4f488523</t>
-  </si>
-  <si>
-    <t>96f72bf71306e328fc99368c6be69005e50f8542</t>
-  </si>
-  <si>
-    <t>6bcdce6703462b574477bce0b455dd22a00e16ea</t>
-  </si>
-  <si>
-    <t>60565b346279343051032a0a004f55306f3fe488</t>
-  </si>
-  <si>
-    <t>40ae1e9fa1f50056bf51c61c2ffef38e8ad80253</t>
-  </si>
-  <si>
-    <t>de6130e27bf62bf5d765159e58174c4d6441ecbd</t>
-  </si>
-  <si>
-    <t>ea534cf2d97afa88cf1c6e6fc5cc4443cd32ebcd</t>
-  </si>
-  <si>
-    <t>e4801d90869cbf1884b2ab73398cac118ffb285d</t>
-  </si>
-  <si>
-    <t>97f2bdac9fcc37144ff88d852282d5064abfcfeb</t>
-  </si>
-  <si>
-    <t>c2a8bee1d8c4ac8aac7b80bccefceb757dd63b97</t>
-  </si>
-  <si>
-    <t>0bc56c4c29bfd4906a9467bddc102bd07482c159</t>
-  </si>
-  <si>
     <t>c46b0bb235abef768f57e415788a288b85684860</t>
   </si>
   <si>
@@ -227,22 +251,22 @@
     <t>13b223656c39c21a277fe932bd7ca7c1a2cab790</t>
   </si>
   <si>
-    <t>735977ee7c6fc0af70b43ec6c2b2d3e23206d14a</t>
-  </si>
-  <si>
-    <t>fda05aac611a7ed8144cb3d6dfe2bb513d07500b</t>
-  </si>
-  <si>
-    <t>6df3d4354ac5f07e0a3df627b085a8d3dccf93c5</t>
-  </si>
-  <si>
-    <t>2c2c93c7f9894ac253e2305e243f8693d6afe16a</t>
-  </si>
-  <si>
-    <t>66226ee68a860cda6530d2869ec7330ac3f2b11d</t>
-  </si>
-  <si>
-    <t>46fbb66cbda0e630a8c574d72316821a41f9d568</t>
+    <t>ea64f9dcfbd8b42ea665a96dfaad67b4297705f3</t>
+  </si>
+  <si>
+    <t>f514abd99a99a21ee60279b799a95290036590a6</t>
+  </si>
+  <si>
+    <t>af3be5f8b6d3774424b4cb9a966ddcd3a4b8e3a4</t>
+  </si>
+  <si>
+    <t>84272b76a91a56ac9f7ad3fd9376f75e521f2268</t>
+  </si>
+  <si>
+    <t>310571247b991149ee8e020bdaa47cbb9e29b36a</t>
+  </si>
+  <si>
+    <t>6fc0aa9827500687be69beaa87baa3b6b49fccc2</t>
   </si>
   <si>
     <t>544453d77af0303f40f634c21c73e591bcd8a6d1</t>
@@ -254,10 +278,49 @@
     <t>d6ae1c3b82410e336938259c9b8aa11967db820e</t>
   </si>
   <si>
-    <t>d193a0c3876a52af0e1f2ab0d9b8d90e9baedcbd</t>
-  </si>
-  <si>
-    <t>de3a1740aef08a4f443bd0e23c8a6745d412a49d</t>
+    <t>96cf31e6213388f86fe575d125602506bc2a5118</t>
+  </si>
+  <si>
+    <t>2ea5ff791ef72b0125e70f2250f49d1aa5ec42eb</t>
+  </si>
+  <si>
+    <t>72eb5afc31656ba92e186f2b2e5834ab1a4c63d7</t>
+  </si>
+  <si>
+    <t>2a434dd01021f780b3316880770835b4ba030ee0</t>
+  </si>
+  <si>
+    <t>5cde236271f0e8320db1752ddb994658c14801d5</t>
+  </si>
+  <si>
+    <t>e502f5d9ade8401036e541b6cfc70314960773c3</t>
+  </si>
+  <si>
+    <t>dd3385cbce7aed4ee56093042bc541e05ce52418</t>
+  </si>
+  <si>
+    <t>414fdbe2d6a98b2d83b13da9c7dd322d2dc2218c</t>
+  </si>
+  <si>
+    <t>5b0f7ff242505f0b65ef4b1b01bb5a205f02b166</t>
+  </si>
+  <si>
+    <t>9570e2a1a850263428870c6215b2d41836169c33</t>
+  </si>
+  <si>
+    <t>a87d9e422d52f9f6cc63871ce09d414ad723c74a</t>
+  </si>
+  <si>
+    <t>3ded47f65da150e54af02ad4489a606734a14ba0</t>
+  </si>
+  <si>
+    <t>90c513cc6b1b263d0fb9491d46a5978299f938a0</t>
+  </si>
+  <si>
+    <t>2410ff2d34ab5ccb269e5861c7636ff9ce02251f</t>
+  </si>
+  <si>
+    <t>396771c14a471c0dc3ec72bc311c8c4573742cad</t>
   </si>
   <si>
     <t>c9cce2c9352f90dca9346f63fe1730ce35bae26f</t>
@@ -266,52 +329,49 @@
     <t>014d27c190bc790030ad65c101ac6fba7392e56f</t>
   </si>
   <si>
-    <t>e502f5d9ade8401036e541b6cfc70314960773c3</t>
-  </si>
-  <si>
-    <t>ea64f9dcfbd8b42ea665a96dfaad67b4297705f3</t>
-  </si>
-  <si>
-    <t>f514abd99a99a21ee60279b799a95290036590a6</t>
-  </si>
-  <si>
-    <t>af3be5f8b6d3774424b4cb9a966ddcd3a4b8e3a4</t>
-  </si>
-  <si>
-    <t>90c513cc6b1b263d0fb9491d46a5978299f938a0</t>
-  </si>
-  <si>
-    <t>2410ff2d34ab5ccb269e5861c7636ff9ce02251f</t>
-  </si>
-  <si>
-    <t>396771c14a471c0dc3ec72bc311c8c4573742cad</t>
-  </si>
-  <si>
-    <t>2a434dd01021f780b3316880770835b4ba030ee0</t>
-  </si>
-  <si>
-    <t>5cde236271f0e8320db1752ddb994658c14801d5</t>
+    <t>7a161eded61193c0871ade7385f4ec15aa5e62b9</t>
+  </si>
+  <si>
+    <t>6c8380d5f8e37f412bcd426218880dafad678895</t>
   </si>
   <si>
     <t>a6f752fbb6a3bb4bc142690ffc473d2223bc2321</t>
   </si>
   <si>
-    <t>7a161eded61193c0871ade7385f4ec15aa5e62b9</t>
-  </si>
-  <si>
-    <t>6c8380d5f8e37f412bcd426218880dafad678895</t>
-  </si>
-  <si>
-    <t>84272b76a91a56ac9f7ad3fd9376f75e521f2268</t>
-  </si>
-  <si>
-    <t>310571247b991149ee8e020bdaa47cbb9e29b36a</t>
-  </si>
-  <si>
-    <t>6fc0aa9827500687be69beaa87baa3b6b49fccc2</t>
-  </si>
-  <si>
-    <t>2ea5ff791ef72b0125e70f2250f49d1aa5ec42eb</t>
+    <t>d17aa559eaaf716b6d12e59e09bc537035208826</t>
+  </si>
+  <si>
+    <t>dad198ac91aa0e0169fe1b36bea896bfb3860db5</t>
+  </si>
+  <si>
+    <t>3a0c40637db6b662f51e33e1fbd45266b681042e</t>
+  </si>
+  <si>
+    <t>4dab61b6a848b502ec006b371af6b6278a2dd585</t>
+  </si>
+  <si>
+    <t>ee2414a8d22d7b296762ad2acd641e70cd579870</t>
+  </si>
+  <si>
+    <t>8a5793a80549ab994d1cd50ddcd741c4957cb326</t>
+  </si>
+  <si>
+    <t>132fe564c906fedd0b8bd5b18e9ada6f2bb8ce36</t>
+  </si>
+  <si>
+    <t>e291c91c5c6bd557b101678611b80776da452b78</t>
+  </si>
+  <si>
+    <t>740f6143cbf25bfad9bfb54e61f2c485b9f4adcc</t>
+  </si>
+  <si>
+    <t>c45fbbb8eb5cb819b12213f807c51e4695f3b80e</t>
+  </si>
+  <si>
+    <t>9e7a0767265924e1ec266ed98820ea9d1cc2499e</t>
+  </si>
+  <si>
+    <t>17f3a429a5c9a243abb61b078d9511c523c3954e</t>
   </si>
   <si>
     <t>f4b76296b85876d2ee247b430e8ab1e575f83b06</t>
@@ -320,30 +380,6 @@
     <t>46542d3804f4a1ad015b236a0ef90af5847ad566</t>
   </si>
   <si>
-    <t>96cf31e6213388f86fe575d125602506bc2a5118</t>
-  </si>
-  <si>
-    <t>72eb5afc31656ba92e186f2b2e5834ab1a4c63d7</t>
-  </si>
-  <si>
-    <t>9570e2a1a850263428870c6215b2d41836169c33</t>
-  </si>
-  <si>
-    <t>a87d9e422d52f9f6cc63871ce09d414ad723c74a</t>
-  </si>
-  <si>
-    <t>3ded47f65da150e54af02ad4489a606734a14ba0</t>
-  </si>
-  <si>
-    <t>c45fbbb8eb5cb819b12213f807c51e4695f3b80e</t>
-  </si>
-  <si>
-    <t>9e7a0767265924e1ec266ed98820ea9d1cc2499e</t>
-  </si>
-  <si>
-    <t>17f3a429a5c9a243abb61b078d9511c523c3954e</t>
-  </si>
-  <si>
     <t>1222a15f8cab9f34373971a569b3b9c1f5e12516</t>
   </si>
   <si>
@@ -362,22 +398,13 @@
     <t>a1390bbc5bbeeecfcbbcff418133ca6564e5ac64</t>
   </si>
   <si>
-    <t>dd3385cbce7aed4ee56093042bc541e05ce52418</t>
-  </si>
-  <si>
-    <t>414fdbe2d6a98b2d83b13da9c7dd322d2dc2218c</t>
-  </si>
-  <si>
-    <t>5b0f7ff242505f0b65ef4b1b01bb5a205f02b166</t>
-  </si>
-  <si>
-    <t>d17aa559eaaf716b6d12e59e09bc537035208826</t>
-  </si>
-  <si>
-    <t>dad198ac91aa0e0169fe1b36bea896bfb3860db5</t>
-  </si>
-  <si>
-    <t>3a0c40637db6b662f51e33e1fbd45266b681042e</t>
+    <t>128f4d6274bb9fee15d6bee635f37da2396e9db2</t>
+  </si>
+  <si>
+    <t>0a81003dd396b155e43f56a07e8b2940da610b2b</t>
+  </si>
+  <si>
+    <t>615b8567f45af4303e3c2ccfa16e6e99e3907978</t>
   </si>
   <si>
     <t>4eb366162caa62f21b99b6c1ce5accd71e89a338</t>
@@ -398,13 +425,13 @@
     <t>4a760ac6866ce1e32f58da1b8deccb38a8914116</t>
   </si>
   <si>
-    <t>132fe564c906fedd0b8bd5b18e9ada6f2bb8ce36</t>
-  </si>
-  <si>
-    <t>e291c91c5c6bd557b101678611b80776da452b78</t>
-  </si>
-  <si>
-    <t>740f6143cbf25bfad9bfb54e61f2c485b9f4adcc</t>
+    <t>be53447f5676c2fe0bf2317955feea01afe9e65e</t>
+  </si>
+  <si>
+    <t>1adc7a128005e76fedfea76f2b71b14e83ebd44b</t>
+  </si>
+  <si>
+    <t>ad08f92972fd1c7c536a8e9644e9fcb4858e069c</t>
   </si>
   <si>
     <t>3092715893fc6716e9943a09ccd48330658386d0</t>
@@ -413,15 +440,6 @@
     <t>cd9cef9e0878937c8ce87de114e3485471fffcd6</t>
   </si>
   <si>
-    <t>be53447f5676c2fe0bf2317955feea01afe9e65e</t>
-  </si>
-  <si>
-    <t>1adc7a128005e76fedfea76f2b71b14e83ebd44b</t>
-  </si>
-  <si>
-    <t>ad08f92972fd1c7c536a8e9644e9fcb4858e069c</t>
-  </si>
-  <si>
     <t>af597cd63d9e0a963fc7af8ad5840f5f21df39ca</t>
   </si>
   <si>
@@ -431,15 +449,6 @@
     <t>1111c8fb4aa10d242a8e9a0601c6a0b2a0075e08</t>
   </si>
   <si>
-    <t>4dab61b6a848b502ec006b371af6b6278a2dd585</t>
-  </si>
-  <si>
-    <t>ee2414a8d22d7b296762ad2acd641e70cd579870</t>
-  </si>
-  <si>
-    <t>8a5793a80549ab994d1cd50ddcd741c4957cb326</t>
-  </si>
-  <si>
     <t>5ce810212b52459526ad1e5e153a04ac0d12223f</t>
   </si>
   <si>
@@ -449,13 +458,55 @@
     <t>e07870d502c6908d6149d5aafc82676304b49d47</t>
   </si>
   <si>
-    <t>128f4d6274bb9fee15d6bee635f37da2396e9db2</t>
-  </si>
-  <si>
-    <t>0a81003dd396b155e43f56a07e8b2940da610b2b</t>
-  </si>
-  <si>
-    <t>615b8567f45af4303e3c2ccfa16e6e99e3907978</t>
+    <t>551f48eeccc4701e3aaecf92c1a5769c64b6bd25</t>
+  </si>
+  <si>
+    <t>abb8bd6afcc3b0fddd7a7ffe2feefa6a9a12bddb</t>
+  </si>
+  <si>
+    <t>f8d0902af27332892c156793a34718ca2d386f94</t>
+  </si>
+  <si>
+    <t>618e0250bbdcd23f3f58acb0343ea7b515caf0c7</t>
+  </si>
+  <si>
+    <t>9e2922db61878d899ff04c8bf7c72a7a3f8f480b</t>
+  </si>
+  <si>
+    <t>73b725e02a109943107aa528b103ca50a4db9647</t>
+  </si>
+  <si>
+    <t>349cdfe83b74ae470bd931823c206c7b938e7442</t>
+  </si>
+  <si>
+    <t>ea6daf13129bd037902c86f2b85081a888c5a2f5</t>
+  </si>
+  <si>
+    <t>bfbccbe3c6a6efff0696a913afcf0057bf178658</t>
+  </si>
+  <si>
+    <t>650d9534a73e10c0df44b80dbe6c6064a59d652a</t>
+  </si>
+  <si>
+    <t>146d0db501d5834b9aead0a3178f60df38383bb8</t>
+  </si>
+  <si>
+    <t>9065c5d86ea8a4de874a9fdaf934ce3d9576779e</t>
+  </si>
+  <si>
+    <t>dac0e93aa42dab74fccdd4fa76579f9f25b6ce4a</t>
+  </si>
+  <si>
+    <t>db3bb2c7a889177354b3b4c61303a36145d923a7</t>
+  </si>
+  <si>
+    <t>498e803b3303994e1da4b190cb7989fe34c1134b</t>
+  </si>
+  <si>
+    <t>741908cc9f74bb0ecdf3c324c6733983a7d6945d</t>
+  </si>
+  <si>
+    <t>7a4addacd24e35b5454a5b82f12745297f98e66b</t>
   </si>
   <si>
     <t>d77a7706866d87f80d5787768c63a2a896173e89</t>
@@ -467,118 +518,67 @@
     <t>aa48a76c22c036e50788e6fbd37d4127059833b7</t>
   </si>
   <si>
-    <t>498e803b3303994e1da4b190cb7989fe34c1134b</t>
-  </si>
-  <si>
-    <t>741908cc9f74bb0ecdf3c324c6733983a7d6945d</t>
-  </si>
-  <si>
-    <t>7a4addacd24e35b5454a5b82f12745297f98e66b</t>
+    <t>67cc06662d9c97c1d8169dde8e3d8399580b382c</t>
+  </si>
+  <si>
+    <t>2b9b7ec33c4e1f8f57f4eaab89c210277244c172</t>
+  </si>
+  <si>
+    <t>036968e556eecbdef356e0802b5928f7f2978516</t>
   </si>
   <si>
     <t>d1428ba1e5a2fb7cc3e05a0e9549011cf2323ca6</t>
   </si>
   <si>
+    <t>d3460734dbc6fbefebfbcc5efc47343a19e20589</t>
+  </si>
+  <si>
+    <t>9c23f065809e8176a846424f382ca835532a203a</t>
+  </si>
+  <si>
+    <t>deb04e9cab29528d8feb7bf18d3ccdb3d64def6c</t>
+  </si>
+  <si>
+    <t>5e7bff42d705ced42cac9e276df4365e49f79031</t>
+  </si>
+  <si>
     <t>8bb9b31da1af3dcefd5b0071c5354029285bd862</t>
   </si>
   <si>
     <t>fcddd5131777f8cb907223ae5d33c96af6151980</t>
   </si>
   <si>
-    <t>618e0250bbdcd23f3f58acb0343ea7b515caf0c7</t>
-  </si>
-  <si>
-    <t>9e2922db61878d899ff04c8bf7c72a7a3f8f480b</t>
-  </si>
-  <si>
-    <t>73b725e02a109943107aa528b103ca50a4db9647</t>
-  </si>
-  <si>
-    <t>650d9534a73e10c0df44b80dbe6c6064a59d652a</t>
-  </si>
-  <si>
-    <t>146d0db501d5834b9aead0a3178f60df38383bb8</t>
-  </si>
-  <si>
-    <t>9065c5d86ea8a4de874a9fdaf934ce3d9576779e</t>
-  </si>
-  <si>
-    <t>67cc06662d9c97c1d8169dde8e3d8399580b382c</t>
-  </si>
-  <si>
-    <t>2b9b7ec33c4e1f8f57f4eaab89c210277244c172</t>
-  </si>
-  <si>
-    <t>036968e556eecbdef356e0802b5928f7f2978516</t>
-  </si>
-  <si>
-    <t>349cdfe83b74ae470bd931823c206c7b938e7442</t>
-  </si>
-  <si>
-    <t>ea6daf13129bd037902c86f2b85081a888c5a2f5</t>
-  </si>
-  <si>
-    <t>bfbccbe3c6a6efff0696a913afcf0057bf178658</t>
+    <t>f87ac42b9326adae43a09ccb44c0e0a6620412bc</t>
+  </si>
+  <si>
+    <t>177f5b2480cfb931f3c7a2988b72f148b0dc6e5f</t>
+  </si>
+  <si>
+    <t>ac465f4d948a7bda5d861f32a50e94023ce0e9d7</t>
+  </si>
+  <si>
+    <t>5b7006993f8c79c3e547b3d09e711f83d31100c8</t>
+  </si>
+  <si>
+    <t>498fd139d4c627b58f52acc56be5730b94ff9e45</t>
+  </si>
+  <si>
+    <t>d9e821ecf0e8842ac5c9c753dec311b2642c4df0</t>
+  </si>
+  <si>
+    <t>d5280c5060e769d14a177fac2074571cc6f007d1</t>
+  </si>
+  <si>
+    <t>2d4cfbaa295ea54734f8a29d0411a01dcf71b213</t>
+  </si>
+  <si>
+    <t>10d1f5480d8fe24ce852bf86dc859261f5e36f1a</t>
   </si>
   <si>
     <t>0e94676d9716710e997d4307cf5857ce44b49622</t>
   </si>
   <si>
-    <t>d5280c5060e769d14a177fac2074571cc6f007d1</t>
-  </si>
-  <si>
     <t>1c832372248621ad861d567cc554d39b2902e72f</t>
-  </si>
-  <si>
-    <t>d3460734dbc6fbefebfbcc5efc47343a19e20589</t>
-  </si>
-  <si>
-    <t>9c23f065809e8176a846424f382ca835532a203a</t>
-  </si>
-  <si>
-    <t>deb04e9cab29528d8feb7bf18d3ccdb3d64def6c</t>
-  </si>
-  <si>
-    <t>5e7bff42d705ced42cac9e276df4365e49f79031</t>
-  </si>
-  <si>
-    <t>dac0e93aa42dab74fccdd4fa76579f9f25b6ce4a</t>
-  </si>
-  <si>
-    <t>db3bb2c7a889177354b3b4c61303a36145d923a7</t>
-  </si>
-  <si>
-    <t>551f48eeccc4701e3aaecf92c1a5769c64b6bd25</t>
-  </si>
-  <si>
-    <t>abb8bd6afcc3b0fddd7a7ffe2feefa6a9a12bddb</t>
-  </si>
-  <si>
-    <t>f8d0902af27332892c156793a34718ca2d386f94</t>
-  </si>
-  <si>
-    <t>5b7006993f8c79c3e547b3d09e711f83d31100c8</t>
-  </si>
-  <si>
-    <t>498fd139d4c627b58f52acc56be5730b94ff9e45</t>
-  </si>
-  <si>
-    <t>d9e821ecf0e8842ac5c9c753dec311b2642c4df0</t>
-  </si>
-  <si>
-    <t>2d4cfbaa295ea54734f8a29d0411a01dcf71b213</t>
-  </si>
-  <si>
-    <t>10d1f5480d8fe24ce852bf86dc859261f5e36f1a</t>
-  </si>
-  <si>
-    <t>f87ac42b9326adae43a09ccb44c0e0a6620412bc</t>
-  </si>
-  <si>
-    <t>177f5b2480cfb931f3c7a2988b72f148b0dc6e5f</t>
-  </si>
-  <si>
-    <t>ac465f4d948a7bda5d861f32a50e94023ce0e9d7</t>
   </si>
   <si>
     <t>ec4f0516359bc640eaecaaebac56c816bce5a250</t>
@@ -678,13 +678,13 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>302.0</v>
+        <v>312.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>180.07000732421875</v>
+        <v>170.1110382080078</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>302.0</v>
+        <v>312.0</v>
       </c>
       <c r="E3" t="n" s="0">
         <v>1.0</v>
@@ -725,24 +725,24 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>184.89996337890625</v>
+        <v>165.0690155029297</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>302.0</v>
+        <v>312.0</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>1.0</v>
@@ -757,30 +757,30 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>184.510986328125</v>
+        <v>160.5780029296875</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>300.0</v>
+        <v>312.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G5" t="b" s="0">
         <v>0</v>
@@ -789,24 +789,24 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>176.0050048828125</v>
+        <v>163.31298828125</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>22</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>299.0</v>
+        <v>312.0</v>
       </c>
       <c r="E6" t="n" s="0">
         <v>1.0</v>
@@ -821,30 +821,30 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>180.4759979248047</v>
+        <v>164.26300048828125</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B7" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>26</v>
-      </c>
       <c r="D7" t="n" s="0">
-        <v>299.0</v>
+        <v>312.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G7" t="b" s="0">
         <v>0</v>
@@ -853,30 +853,30 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>187.59800720214844</v>
+        <v>169.79502868652344</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B8" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>29</v>
-      </c>
       <c r="D8" t="n" s="0">
-        <v>299.0</v>
+        <v>312.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G8" t="b" s="0">
         <v>0</v>
@@ -885,30 +885,30 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>297.653076171875</v>
+        <v>166.3760223388672</v>
       </c>
       <c r="J8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="B9" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>17</v>
-      </c>
       <c r="D9" t="n" s="0">
-        <v>302.0</v>
+        <v>312.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G9" t="b" s="0">
         <v>0</v>
@@ -917,30 +917,30 @@
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>294.7601318359375</v>
+        <v>169.57000732421875</v>
       </c>
       <c r="J9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="B10" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>34</v>
-      </c>
       <c r="D10" t="n" s="0">
-        <v>302.0</v>
+        <v>312.0</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G10" t="b" s="0">
         <v>0</v>
@@ -949,30 +949,30 @@
         <v>1</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>294.0421142578125</v>
+        <v>171.3890380859375</v>
       </c>
       <c r="J10" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="B11" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>37</v>
-      </c>
       <c r="D11" t="n" s="0">
-        <v>299.0</v>
+        <v>308.0</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G11" t="b" s="0">
         <v>0</v>
@@ -981,30 +981,30 @@
         <v>1</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>184.03102111816406</v>
+        <v>163.38597106933594</v>
       </c>
       <c r="J11" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="B12" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>40</v>
-      </c>
       <c r="D12" t="n" s="0">
-        <v>302.0</v>
+        <v>308.0</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G12" t="b" s="0">
         <v>0</v>
@@ -1013,30 +1013,30 @@
         <v>1</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>297.2880859375</v>
+        <v>170.5330352783203</v>
       </c>
       <c r="J12" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="B13" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="C13" t="s" s="0">
-        <v>43</v>
-      </c>
       <c r="D13" t="n" s="0">
-        <v>299.0</v>
+        <v>339.0</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G13" t="b" s="0">
         <v>0</v>
@@ -1045,30 +1045,30 @@
         <v>1</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>260.5171813964844</v>
+        <v>186.1949920654297</v>
       </c>
       <c r="J13" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="B14" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="C14" t="s" s="0">
-        <v>46</v>
-      </c>
       <c r="D14" t="n" s="0">
-        <v>302.0</v>
+        <v>333.0</v>
       </c>
       <c r="E14" t="n" s="0">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G14" t="b" s="0">
         <v>0</v>
@@ -1077,24 +1077,24 @@
         <v>1</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>176.10000610351562</v>
+        <v>173.8400115966797</v>
       </c>
       <c r="J14" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="B15" t="s" s="0">
-        <v>48</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>49</v>
-      </c>
       <c r="D15" t="n" s="0">
-        <v>300.0</v>
+        <v>333.0</v>
       </c>
       <c r="E15" t="n" s="0">
         <v>1.0</v>
@@ -1109,30 +1109,30 @@
         <v>1</v>
       </c>
       <c r="I15" t="n" s="0">
-        <v>179.08700561523438</v>
+        <v>180.4810028076172</v>
       </c>
       <c r="J15" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="B16" t="s" s="0">
-        <v>51</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>52</v>
-      </c>
       <c r="D16" t="n" s="0">
-        <v>299.0</v>
+        <v>333.0</v>
       </c>
       <c r="E16" t="n" s="0">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G16" t="b" s="0">
         <v>0</v>
@@ -1141,24 +1141,24 @@
         <v>1</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>161.43698120117188</v>
+        <v>197.001953125</v>
       </c>
       <c r="J16" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="B17" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>55</v>
-      </c>
       <c r="D17" t="n" s="0">
-        <v>299.0</v>
+        <v>339.0</v>
       </c>
       <c r="E17" t="n" s="0">
         <v>6.0</v>
@@ -1173,24 +1173,24 @@
         <v>1</v>
       </c>
       <c r="I17" t="n" s="0">
-        <v>172.6260223388672</v>
+        <v>176.3790283203125</v>
       </c>
       <c r="J17" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="C18" t="s" s="0">
-        <v>57</v>
-      </c>
       <c r="D18" t="n" s="0">
-        <v>299.0</v>
+        <v>339.0</v>
       </c>
       <c r="E18" t="n" s="0">
         <v>1.0</v>
@@ -1205,30 +1205,30 @@
         <v>1</v>
       </c>
       <c r="I18" t="n" s="0">
-        <v>170.38699340820312</v>
+        <v>184.3400421142578</v>
       </c>
       <c r="J18" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>302.0</v>
+        <v>339.0</v>
       </c>
       <c r="E19" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G19" t="b" s="0">
         <v>0</v>
@@ -1237,30 +1237,30 @@
         <v>1</v>
       </c>
       <c r="I19" t="n" s="0">
-        <v>256.8599853515625</v>
+        <v>179.16000366210938</v>
       </c>
       <c r="J19" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>299.0</v>
+        <v>339.0</v>
       </c>
       <c r="E20" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G20" t="b" s="0">
         <v>0</v>
@@ -1269,30 +1269,30 @@
         <v>1</v>
       </c>
       <c r="I20" t="n" s="0">
-        <v>246.77003479003906</v>
+        <v>180.32000732421875</v>
       </c>
       <c r="J20" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>302.0</v>
+        <v>339.0</v>
       </c>
       <c r="E21" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G21" t="b" s="0">
         <v>0</v>
@@ -1301,10 +1301,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n" s="0">
-        <v>255.28311157226562</v>
+        <v>184.22702026367188</v>
       </c>
       <c r="J21" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1312,19 +1312,19 @@
         <v>65</v>
       </c>
       <c r="B22" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C22" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="C22" t="s" s="0">
-        <v>67</v>
-      </c>
       <c r="D22" t="n" s="0">
-        <v>295.0</v>
+        <v>339.0</v>
       </c>
       <c r="E22" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G22" t="b" s="0">
         <v>0</v>
@@ -1333,30 +1333,30 @@
         <v>1</v>
       </c>
       <c r="I22" t="n" s="0">
-        <v>153.0500030517578</v>
+        <v>183.7799835205078</v>
       </c>
       <c r="J22" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B23" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="B23" t="s" s="0">
+      <c r="C23" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="C23" t="s" s="0">
-        <v>70</v>
-      </c>
       <c r="D23" t="n" s="0">
-        <v>295.0</v>
+        <v>339.0</v>
       </c>
       <c r="E23" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G23" t="b" s="0">
         <v>0</v>
@@ -1365,30 +1365,30 @@
         <v>1</v>
       </c>
       <c r="I23" t="n" s="0">
-        <v>159.2699737548828</v>
+        <v>184.6840362548828</v>
       </c>
       <c r="J23" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s" s="0">
         <v>71</v>
       </c>
-      <c r="B24" t="s" s="0">
+      <c r="C24" t="s" s="0">
         <v>72</v>
       </c>
-      <c r="C24" t="s" s="0">
-        <v>73</v>
-      </c>
       <c r="D24" t="n" s="0">
-        <v>295.0</v>
+        <v>339.0</v>
       </c>
       <c r="E24" t="n" s="0">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G24" t="b" s="0">
         <v>0</v>
@@ -1397,30 +1397,30 @@
         <v>1</v>
       </c>
       <c r="I24" t="n" s="0">
-        <v>241.9430389404297</v>
+        <v>182.697998046875</v>
       </c>
       <c r="J24" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B25" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B25" t="s" s="0">
+      <c r="C25" t="s" s="0">
         <v>75</v>
       </c>
-      <c r="C25" t="s" s="0">
-        <v>76</v>
-      </c>
       <c r="D25" t="n" s="0">
-        <v>295.0</v>
+        <v>339.0</v>
       </c>
       <c r="E25" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G25" t="b" s="0">
         <v>0</v>
@@ -1429,24 +1429,24 @@
         <v>1</v>
       </c>
       <c r="I25" t="n" s="0">
-        <v>156.04598999023438</v>
+        <v>182.09898376464844</v>
       </c>
       <c r="J25" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s" s="0">
         <v>77</v>
       </c>
-      <c r="B26" t="s" s="0">
+      <c r="C26" t="s" s="0">
         <v>78</v>
       </c>
-      <c r="C26" t="s" s="0">
-        <v>79</v>
-      </c>
       <c r="D26" t="n" s="0">
-        <v>295.0</v>
+        <v>333.0</v>
       </c>
       <c r="E26" t="n" s="0">
         <v>1.0</v>
@@ -1461,30 +1461,30 @@
         <v>1</v>
       </c>
       <c r="I26" t="n" s="0">
-        <v>157.6160125732422</v>
+        <v>206.3839874267578</v>
       </c>
       <c r="J26" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="B27" t="s" s="0">
+      <c r="C27" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="C27" t="s" s="0">
-        <v>50</v>
-      </c>
       <c r="D27" t="n" s="0">
-        <v>299.0</v>
+        <v>333.0</v>
       </c>
       <c r="E27" t="n" s="0">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="F27" t="n" s="0">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="G27" t="b" s="0">
         <v>0</v>
@@ -1493,10 +1493,10 @@
         <v>1</v>
       </c>
       <c r="I27" t="n" s="0">
-        <v>246.77003479003906</v>
+        <v>209.03302001953125</v>
       </c>
       <c r="J27" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1510,13 +1510,13 @@
         <v>84</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>290.0</v>
+        <v>332.0</v>
       </c>
       <c r="E28" t="n" s="0">
-        <v>1.0</v>
+        <v>33.0</v>
       </c>
       <c r="F28" t="n" s="0">
-        <v>1.0</v>
+        <v>33.0</v>
       </c>
       <c r="G28" t="b" s="0">
         <v>0</v>
@@ -1525,10 +1525,10 @@
         <v>1</v>
       </c>
       <c r="I28" t="n" s="0">
-        <v>151.37799072265625</v>
+        <v>189.89202880859375</v>
       </c>
       <c r="J28" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1542,13 +1542,13 @@
         <v>87</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>295.0</v>
+        <v>332.0</v>
       </c>
       <c r="E29" t="n" s="0">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="F29" t="n" s="0">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="G29" t="b" s="0">
         <v>0</v>
@@ -1557,10 +1557,10 @@
         <v>1</v>
       </c>
       <c r="I29" t="n" s="0">
-        <v>243.64805603027344</v>
+        <v>200.66802978515625</v>
       </c>
       <c r="J29" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1574,13 +1574,13 @@
         <v>90</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>290.0</v>
+        <v>293.0</v>
       </c>
       <c r="E30" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F30" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G30" t="b" s="0">
         <v>0</v>
@@ -1589,10 +1589,10 @@
         <v>1</v>
       </c>
       <c r="I30" t="n" s="0">
-        <v>149.031982421875</v>
+        <v>174.20201110839844</v>
       </c>
       <c r="J30" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1603,10 +1603,10 @@
         <v>92</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>288.0</v>
+        <v>327.0</v>
       </c>
       <c r="E31" t="n" s="0">
         <v>1.0</v>
@@ -1621,30 +1621,30 @@
         <v>1</v>
       </c>
       <c r="I31" t="n" s="0">
-        <v>223.87001037597656</v>
+        <v>176.34498596191406</v>
       </c>
       <c r="J31" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>290.0</v>
+        <v>295.0</v>
       </c>
       <c r="E32" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F32" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G32" t="b" s="0">
         <v>0</v>
@@ -1653,30 +1653,30 @@
         <v>1</v>
       </c>
       <c r="I32" t="n" s="0">
-        <v>228.65603637695312</v>
+        <v>172.4740447998047</v>
       </c>
       <c r="J32" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>290.0</v>
+        <v>329.0</v>
       </c>
       <c r="E33" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F33" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G33" t="b" s="0">
         <v>0</v>
@@ -1685,30 +1685,30 @@
         <v>1</v>
       </c>
       <c r="I33" t="n" s="0">
-        <v>150.91201782226562</v>
+        <v>181.8760223388672</v>
       </c>
       <c r="J33" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>295.0</v>
+        <v>329.0</v>
       </c>
       <c r="E34" t="n" s="0">
-        <v>33.0</v>
+        <v>1.0</v>
       </c>
       <c r="F34" t="n" s="0">
-        <v>33.0</v>
+        <v>1.0</v>
       </c>
       <c r="G34" t="b" s="0">
         <v>0</v>
@@ -1717,30 +1717,30 @@
         <v>1</v>
       </c>
       <c r="I34" t="n" s="0">
-        <v>251.1690216064453</v>
+        <v>182.114013671875</v>
       </c>
       <c r="J34" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>288.0</v>
+        <v>329.0</v>
       </c>
       <c r="E35" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F35" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G35" t="b" s="0">
         <v>0</v>
@@ -1749,27 +1749,27 @@
         <v>1</v>
       </c>
       <c r="I35" t="n" s="0">
-        <v>226.7750244140625</v>
+        <v>175.50201416015625</v>
       </c>
       <c r="J35" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>288.0</v>
+        <v>329.0</v>
       </c>
       <c r="E36" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F36" t="n" s="0">
         <v>3.0</v>
@@ -1781,30 +1781,30 @@
         <v>1</v>
       </c>
       <c r="I36" t="n" s="0">
-        <v>150.1439971923828</v>
+        <v>185.55703735351562</v>
       </c>
       <c r="J36" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B37" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="B37" t="s" s="0">
-        <v>105</v>
-      </c>
       <c r="C37" t="s" s="0">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>290.0</v>
+        <v>329.0</v>
       </c>
       <c r="E37" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F37" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G37" t="b" s="0">
         <v>0</v>
@@ -1813,30 +1813,30 @@
         <v>1</v>
       </c>
       <c r="I37" t="n" s="0">
-        <v>227.92906188964844</v>
+        <v>183.99501037597656</v>
       </c>
       <c r="J37" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>288.0</v>
+        <v>284.0</v>
       </c>
       <c r="E38" t="n" s="0">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="F38" t="n" s="0">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G38" t="b" s="0">
         <v>0</v>
@@ -1845,30 +1845,30 @@
         <v>1</v>
       </c>
       <c r="I38" t="n" s="0">
-        <v>149.12298583984375</v>
+        <v>196.23199462890625</v>
       </c>
       <c r="J38" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>288.0</v>
+        <v>284.0</v>
       </c>
       <c r="E39" t="n" s="0">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="F39" t="n" s="0">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G39" t="b" s="0">
         <v>0</v>
@@ -1877,30 +1877,30 @@
         <v>1</v>
       </c>
       <c r="I39" t="n" s="0">
-        <v>147.90696716308594</v>
+        <v>196.66598510742188</v>
       </c>
       <c r="J39" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>288.0</v>
+        <v>293.0</v>
       </c>
       <c r="E40" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F40" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G40" t="b" s="0">
         <v>0</v>
@@ -1909,30 +1909,30 @@
         <v>1</v>
       </c>
       <c r="I40" t="n" s="0">
-        <v>216.35499572753906</v>
+        <v>208.5389862060547</v>
       </c>
       <c r="J40" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>290.0</v>
+        <v>293.0</v>
       </c>
       <c r="E41" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="F41" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="G41" t="b" s="0">
         <v>0</v>
@@ -1941,15 +1941,15 @@
         <v>1</v>
       </c>
       <c r="I41" t="n" s="0">
-        <v>221.3440399169922</v>
+        <v>224.8889923095703</v>
       </c>
       <c r="J41" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>120</v>
@@ -1958,13 +1958,13 @@
         <v>121</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>259.0</v>
+        <v>293.0</v>
       </c>
       <c r="E42" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F42" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G42" t="b" s="0">
         <v>0</v>
@@ -1973,10 +1973,10 @@
         <v>1</v>
       </c>
       <c r="I42" t="n" s="0">
-        <v>230.8070526123047</v>
+        <v>233.80799865722656</v>
       </c>
       <c r="J42" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1990,13 +1990,13 @@
         <v>124</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>288.0</v>
+        <v>293.0</v>
       </c>
       <c r="E43" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="F43" t="n" s="0">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
       <c r="G43" t="b" s="0">
         <v>0</v>
@@ -2005,10 +2005,10 @@
         <v>1</v>
       </c>
       <c r="I43" t="n" s="0">
-        <v>207.65602111816406</v>
+        <v>216.55503845214844</v>
       </c>
       <c r="J43" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2022,13 +2022,13 @@
         <v>127</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>288.0</v>
+        <v>293.0</v>
       </c>
       <c r="E44" t="n" s="0">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="F44" t="n" s="0">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G44" t="b" s="0">
         <v>0</v>
@@ -2037,10 +2037,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n" s="0">
-        <v>210.55503845214844</v>
+        <v>212.81602478027344</v>
       </c>
       <c r="J44" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2054,7 +2054,7 @@
         <v>130</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>288.0</v>
+        <v>293.0</v>
       </c>
       <c r="E45" t="n" s="0">
         <v>2.0</v>
@@ -2069,30 +2069,30 @@
         <v>1</v>
       </c>
       <c r="I45" t="n" s="0">
-        <v>209.718994140625</v>
+        <v>211.3090057373047</v>
       </c>
       <c r="J45" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>288.0</v>
+        <v>293.0</v>
       </c>
       <c r="E46" t="n" s="0">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="F46" t="n" s="0">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G46" t="b" s="0">
         <v>0</v>
@@ -2101,30 +2101,30 @@
         <v>1</v>
       </c>
       <c r="I46" t="n" s="0">
-        <v>211.4240264892578</v>
+        <v>212.63002014160156</v>
       </c>
       <c r="J46" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>288.0</v>
+        <v>293.0</v>
       </c>
       <c r="E47" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="F47" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G47" t="b" s="0">
         <v>0</v>
@@ -2133,24 +2133,24 @@
         <v>1</v>
       </c>
       <c r="I47" t="n" s="0">
-        <v>137.176025390625</v>
+        <v>205.95103454589844</v>
       </c>
       <c r="J47" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>288.0</v>
+        <v>293.0</v>
       </c>
       <c r="E48" t="n" s="0">
         <v>1.0</v>
@@ -2165,15 +2165,15 @@
         <v>1</v>
       </c>
       <c r="I48" t="n" s="0">
-        <v>140.718994140625</v>
+        <v>204.86203002929688</v>
       </c>
       <c r="J48" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B49" t="s" s="0">
         <v>140</v>
@@ -2182,13 +2182,13 @@
         <v>141</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>255.0</v>
+        <v>293.0</v>
       </c>
       <c r="E49" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F49" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G49" t="b" s="0">
         <v>0</v>
@@ -2197,10 +2197,10 @@
         <v>1</v>
       </c>
       <c r="I49" t="n" s="0">
-        <v>226.78904724121094</v>
+        <v>214.60800170898438</v>
       </c>
       <c r="J49" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2214,13 +2214,13 @@
         <v>144</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>235.0</v>
+        <v>293.0</v>
       </c>
       <c r="E50" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F50" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G50" t="b" s="0">
         <v>0</v>
@@ -2229,10 +2229,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n" s="0">
-        <v>115.87197875976562</v>
+        <v>210.7050018310547</v>
       </c>
       <c r="J50" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2246,7 +2246,7 @@
         <v>147</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>288.0</v>
+        <v>277.0</v>
       </c>
       <c r="E51" t="n" s="0">
         <v>2.0</v>
@@ -2261,10 +2261,10 @@
         <v>1</v>
       </c>
       <c r="I51" t="n" s="0">
-        <v>211.48904418945312</v>
+        <v>152.68499755859375</v>
       </c>
       <c r="J51" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2278,7 +2278,7 @@
         <v>150</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>279.0</v>
+        <v>277.0</v>
       </c>
       <c r="E52" t="n" s="0">
         <v>1.0</v>
@@ -2293,10 +2293,10 @@
         <v>1</v>
       </c>
       <c r="I52" t="n" s="0">
-        <v>211.7500457763672</v>
+        <v>156.17401123046875</v>
       </c>
       <c r="J52" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2310,7 +2310,7 @@
         <v>153</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>275.0</v>
+        <v>284.0</v>
       </c>
       <c r="E53" t="n" s="0">
         <v>2.0</v>
@@ -2325,10 +2325,10 @@
         <v>1</v>
       </c>
       <c r="I53" t="n" s="0">
-        <v>151.04698181152344</v>
+        <v>196.7160186767578</v>
       </c>
       <c r="J53" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2342,13 +2342,13 @@
         <v>156</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>234.0</v>
+        <v>277.0</v>
       </c>
       <c r="E54" t="n" s="0">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F54" t="n" s="0">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G54" t="b" s="0">
         <v>0</v>
@@ -2357,10 +2357,10 @@
         <v>1</v>
       </c>
       <c r="I54" t="n" s="0">
-        <v>115.93998718261719</v>
+        <v>151.80502319335938</v>
       </c>
       <c r="J54" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2374,13 +2374,13 @@
         <v>159</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>279.0</v>
+        <v>277.0</v>
       </c>
       <c r="E55" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F55" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G55" t="b" s="0">
         <v>0</v>
@@ -2389,10 +2389,10 @@
         <v>1</v>
       </c>
       <c r="I55" t="n" s="0">
-        <v>213.4310302734375</v>
+        <v>153.1940155029297</v>
       </c>
       <c r="J55" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2400,13 +2400,13 @@
         <v>160</v>
       </c>
       <c r="B56" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="C56" t="s" s="0">
         <v>161</v>
       </c>
-      <c r="C56" t="s" s="0">
-        <v>162</v>
-      </c>
       <c r="D56" t="n" s="0">
-        <v>235.0</v>
+        <v>277.0</v>
       </c>
       <c r="E56" t="n" s="0">
         <v>1.0</v>
@@ -2421,30 +2421,30 @@
         <v>1</v>
       </c>
       <c r="I56" t="n" s="0">
-        <v>118.43497467041016</v>
+        <v>157.0460205078125</v>
       </c>
       <c r="J56" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B57" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="B57" t="s" s="0">
+      <c r="C57" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="C57" t="s" s="0">
-        <v>165</v>
-      </c>
       <c r="D57" t="n" s="0">
-        <v>272.0</v>
+        <v>280.0</v>
       </c>
       <c r="E57" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F57" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G57" t="b" s="0">
         <v>0</v>
@@ -2453,30 +2453,30 @@
         <v>1</v>
       </c>
       <c r="I57" t="n" s="0">
-        <v>155.7510223388672</v>
+        <v>198.4320068359375</v>
       </c>
       <c r="J57" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="B58" t="s" s="0">
         <v>166</v>
       </c>
-      <c r="B58" t="s" s="0">
+      <c r="C58" t="s" s="0">
         <v>167</v>
       </c>
-      <c r="C58" t="s" s="0">
-        <v>168</v>
-      </c>
       <c r="D58" t="n" s="0">
-        <v>235.0</v>
+        <v>284.0</v>
       </c>
       <c r="E58" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F58" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G58" t="b" s="0">
         <v>0</v>
@@ -2485,30 +2485,30 @@
         <v>1</v>
       </c>
       <c r="I58" t="n" s="0">
-        <v>155.97996520996094</v>
+        <v>191.88900756835938</v>
       </c>
       <c r="J58" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B59" t="s" s="0">
         <v>169</v>
       </c>
-      <c r="B59" t="s" s="0">
+      <c r="C59" t="s" s="0">
         <v>170</v>
       </c>
-      <c r="C59" t="s" s="0">
-        <v>171</v>
-      </c>
       <c r="D59" t="n" s="0">
-        <v>234.0</v>
+        <v>277.0</v>
       </c>
       <c r="E59" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="F59" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G59" t="b" s="0">
         <v>0</v>
@@ -2517,24 +2517,24 @@
         <v>1</v>
       </c>
       <c r="I59" t="n" s="0">
-        <v>109.24098205566406</v>
+        <v>191.74400329589844</v>
       </c>
       <c r="J59" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C60" t="s" s="0">
         <v>172</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>235.0</v>
+        <v>277.0</v>
       </c>
       <c r="E60" t="n" s="0">
         <v>3.0</v>
@@ -2549,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I60" t="n" s="0">
-        <v>117.78199005126953</v>
+        <v>166.46302795410156</v>
       </c>
       <c r="J60" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2566,7 +2566,7 @@
         <v>175</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>272.0</v>
+        <v>277.0</v>
       </c>
       <c r="E61" t="n" s="0">
         <v>2.0</v>
@@ -2581,30 +2581,30 @@
         <v>1</v>
       </c>
       <c r="I61" t="n" s="0">
-        <v>151.71302795410156</v>
+        <v>183.37698364257812</v>
       </c>
       <c r="J61" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="B62" t="s" s="0">
         <v>176</v>
-      </c>
-      <c r="B62" t="s" s="0">
-        <v>160</v>
       </c>
       <c r="C62" t="s" s="0">
         <v>177</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>235.0</v>
+        <v>276.0</v>
       </c>
       <c r="E62" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="F62" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G62" t="b" s="0">
         <v>0</v>
@@ -2613,10 +2613,10 @@
         <v>1</v>
       </c>
       <c r="I62" t="n" s="0">
-        <v>147.93499755859375</v>
+        <v>128.98300170898438</v>
       </c>
       <c r="J62" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2630,7 +2630,7 @@
         <v>180</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>235.0</v>
+        <v>276.0</v>
       </c>
       <c r="E63" t="n" s="0">
         <v>1.0</v>
@@ -2645,10 +2645,10 @@
         <v>1</v>
       </c>
       <c r="I63" t="n" s="0">
-        <v>140.91798400878906</v>
+        <v>118.98500061035156</v>
       </c>
       <c r="J63" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2662,7 +2662,7 @@
         <v>183</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>234.0</v>
+        <v>276.0</v>
       </c>
       <c r="E64" t="n" s="0">
         <v>1.0</v>
@@ -2677,24 +2677,24 @@
         <v>1</v>
       </c>
       <c r="I64" t="n" s="0">
-        <v>121.88700103759766</v>
+        <v>127.21699523925781</v>
       </c>
       <c r="J64" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C65" t="s" s="0">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>234.0</v>
+        <v>276.0</v>
       </c>
       <c r="E65" t="n" s="0">
         <v>1.0</v>
@@ -2709,30 +2709,30 @@
         <v>1</v>
       </c>
       <c r="I65" t="n" s="0">
-        <v>82.87699890136719</v>
+        <v>119.52201080322266</v>
       </c>
       <c r="J65" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C66" t="s" s="0">
         <v>188</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>234.0</v>
+        <v>276.0</v>
       </c>
       <c r="E66" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F66" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G66" t="b" s="0">
         <v>0</v>
@@ -2741,24 +2741,24 @@
         <v>1</v>
       </c>
       <c r="I66" t="n" s="0">
-        <v>91.83499145507812</v>
+        <v>121.6619873046875</v>
       </c>
       <c r="J66" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C67" t="s" s="0">
         <v>189</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>234.0</v>
+        <v>276.0</v>
       </c>
       <c r="E67" t="n" s="0">
         <v>1.0</v>
@@ -2773,10 +2773,10 @@
         <v>1</v>
       </c>
       <c r="I67" t="n" s="0">
-        <v>106.86499786376953</v>
+        <v>124.18498229980469</v>
       </c>
       <c r="J67" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2787,10 +2787,10 @@
         <v>191</v>
       </c>
       <c r="C68" t="s" s="0">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>234.0</v>
+        <v>276.0</v>
       </c>
       <c r="E68" t="n" s="0">
         <v>2.0</v>
@@ -2805,10 +2805,10 @@
         <v>1</v>
       </c>
       <c r="I68" t="n" s="0">
-        <v>80.16500091552734</v>
+        <v>121.35398864746094</v>
       </c>
       <c r="J68" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
